--- a/artfynd/A 26965-2023 artfynd.xlsx
+++ b/artfynd/A 26965-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26965-2023 artfynd.xlsx
+++ b/artfynd/A 26965-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>153024</v>
       </c>
       <c r="B2" t="n">
-        <v>97636</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464517.4678989724</v>
+        <v>464517</v>
       </c>
       <c r="R2" t="n">
-        <v>6236632.359363493</v>
+        <v>6236632</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,19 +752,9 @@
           <t>2012-09-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -803,6 +788,354 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>153025</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100475</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>522</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sjötåtel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Deschampsia setacea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Huds.) Hack.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Raslången. Västerviksnäs, nordspetsen, 600 m SO., Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>464606</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6236771</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vånga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2012-09-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2012-09-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>64 fertila, 94 strån, 33 sterila ex.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>sjöstrand</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Åke Svensson, Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>153026</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100475</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>522</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sjötåtel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Deschampsia setacea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Huds.) Hack.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Raslången. Västerviksnäs, nordspetsen, 550 m SO., Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>464593</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6236862</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vånga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2012-09-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2012-09-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>14 fertila, 31 strån, 20 sterila ex.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>sjöstrand</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Åke Svensson, Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>153027</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100475</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>522</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sjötåtel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Deschampsia setacea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Huds.) Hack.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Raslången. Västerviksnäs, nordspetsen, 550 m SO., Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>464539</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6236904</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vånga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2012-09-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2012-09-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>en fertil, ett strå, 2 sterila ex.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>blockrik, stenig sjöstrand</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Åke Svensson, Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26965-2023 artfynd.xlsx
+++ b/artfynd/A 26965-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/153024</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/153025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/153026</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,8 +1156,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/153027</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>